--- a/InputData/elec/BGCL/BAU Generation Capacity Lifetime.xlsx
+++ b/InputData/elec/BGCL/BAU Generation Capacity Lifetime.xlsx
@@ -1,27 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BGCL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BGCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{057A7473-9501-4192-B595-7A0EAB14DFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CB9732-B63E-47AC-B933-11538DD711D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8595" yWindow="555" windowWidth="15300" windowHeight="16845" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="2" r:id="rId1"/>
-    <sheet name="EIA Plant Lifetimes" sheetId="3" r:id="rId2"/>
-    <sheet name="BGCL" sheetId="4" r:id="rId3"/>
+    <sheet name="About" sheetId="1" r:id="rId1"/>
+    <sheet name="EIA Plant Lifetimes" sheetId="2" r:id="rId2"/>
+    <sheet name="BGCL" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,59 +35,113 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+  <si>
+    <t>BGCL BAU Generation Capacity Lifetime</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>All Sources</t>
+  </si>
+  <si>
     <t>Energy Information Administration</t>
   </si>
   <si>
-    <t>BGCL BAU Generation Capacity Lifetime</t>
+    <t>Capital Cost and Performance Characteristic Estimates for Utility Sceal Electric Power Generating Technologies</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/analysis/studies/powerplants/capitalcost/pdf/capital_cost_AEO2020.pdf</t>
   </si>
   <si>
     <t>Page 157, Figure 113</t>
   </si>
   <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>This variable represents the lifetimes of different power plant types.</t>
+  </si>
+  <si>
+    <t>We consider the lifetime of petroleum (oil) - burning plants to be the same as natural gas</t>
+  </si>
+  <si>
+    <t>and coal plants.</t>
+  </si>
+  <si>
+    <t>We assume lignite plants have the same lifetime as hard coal plants and that offshore plants have</t>
+  </si>
+  <si>
+    <t>the same lifetime as onshore wind plants.</t>
+  </si>
+  <si>
+    <t>Plant Type</t>
+  </si>
+  <si>
+    <t>Lifetime (yr)</t>
+  </si>
+  <si>
+    <t>UCS Coal w/o CCUS</t>
+  </si>
+  <si>
     <t>Combustion Turbine</t>
   </si>
   <si>
     <t>Combined Cycle</t>
   </si>
   <si>
+    <t>Advanced Nuclear</t>
+  </si>
+  <si>
     <t>Biomass</t>
   </si>
   <si>
     <t>Geothermal</t>
   </si>
   <si>
+    <t>Hydro</t>
+  </si>
+  <si>
     <t>Wind (onshore)</t>
   </si>
   <si>
+    <t>Wind(offshore)</t>
+  </si>
+  <si>
     <t>Solar Thermal</t>
   </si>
   <si>
     <t>Solar PV</t>
   </si>
   <si>
-    <t>Plant Type</t>
-  </si>
-  <si>
-    <t>Lifetime (yr)</t>
-  </si>
-  <si>
-    <t>Hydro</t>
-  </si>
-  <si>
     <t>Electricity Source</t>
   </si>
   <si>
+    <t>Lifetime (years)</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
     <t>nuclear</t>
   </si>
   <si>
     <t>hydro</t>
   </si>
   <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
     <t>solar PV</t>
   </si>
   <si>
@@ -100,9 +151,6 @@
     <t>biomass</t>
   </si>
   <si>
-    <t>natural gas nonpeaker</t>
-  </si>
-  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -112,33 +160,12 @@
     <t>natural gas peaker</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>We consider the lifetime of petroleum (oil) - burning plants to be the same as natural gas</t>
-  </si>
-  <si>
-    <t>and coal plants.</t>
-  </si>
-  <si>
     <t>lignite</t>
   </si>
   <si>
     <t>offshore wind</t>
   </si>
   <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>We assume lignite plants have the same lifetime as hard coal plants and that offshore plants have</t>
-  </si>
-  <si>
-    <t>the same lifetime as onshore wind plants.</t>
-  </si>
-  <si>
     <t>crude oil</t>
   </si>
   <si>
@@ -148,38 +175,32 @@
     <t>municipal solid waste</t>
   </si>
   <si>
-    <t>Lifetime (years)</t>
-  </si>
-  <si>
-    <t>This variable represents the lifetimes of different power plant types.</t>
-  </si>
-  <si>
-    <t>Capital Cost and Performance Characteristic Estimates for Utility Sceal Electric Power Generating Technologies</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/analysis/studies/powerplants/capitalcost/pdf/capital_cost_AEO2020.pdf</t>
-  </si>
-  <si>
-    <t>UCS Coal w/o CCUS</t>
-  </si>
-  <si>
-    <t>Advanced Nuclear</t>
-  </si>
-  <si>
-    <t>Wind(offshore)</t>
-  </si>
-  <si>
-    <t>All Sources</t>
-  </si>
-  <si>
-    <t>Iowa</t>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,6 +220,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -229,7 +257,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -243,7 +271,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -525,92 +555,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="78.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="7">
-        <v>44832</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="B3" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
 
@@ -625,15 +655,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>40</v>
@@ -641,7 +671,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>40</v>
@@ -649,7 +679,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>40</v>
@@ -657,7 +687,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>40</v>
@@ -665,7 +695,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>40</v>
@@ -673,7 +703,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>40</v>
@@ -681,7 +711,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>50</v>
@@ -689,7 +719,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>25</v>
@@ -697,7 +727,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>25</v>
@@ -705,7 +735,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>30</v>
@@ -713,7 +743,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>30</v>
@@ -725,28 +755,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <f>'EIA Plant Lifetimes'!B2</f>
@@ -755,7 +785,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <f>'EIA Plant Lifetimes'!B4</f>
@@ -764,135 +794,204 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B4">
-        <f>'EIA Plant Lifetimes'!B5</f>
+        <f>'EIA Plant Lifetimes'!B4</f>
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="6">
+        <v>32</v>
+      </c>
+      <c r="B5">
+        <f>'EIA Plant Lifetimes'!B5</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="6">
         <f>'EIA Plant Lifetimes'!B8</f>
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7">
         <f>'EIA Plant Lifetimes'!B9</f>
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8">
         <f>'EIA Plant Lifetimes'!B12</f>
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
         <f>'EIA Plant Lifetimes'!B11</f>
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9">
-        <f>'EIA Plant Lifetimes'!B6</f>
-        <v>40</v>
-      </c>
-    </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B10">
-        <f>'EIA Plant Lifetimes'!B7</f>
+        <f>'EIA Plant Lifetimes'!B6</f>
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B11">
-        <f>AVERAGE('EIA Plant Lifetimes'!B2:B4)</f>
+        <f>'EIA Plant Lifetimes'!B7</f>
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B12">
-        <f>'EIA Plant Lifetimes'!B3</f>
+        <f>AVERAGE('EIA Plant Lifetimes'!B2:B4)</f>
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B13">
-        <f>B2</f>
+        <f>'EIA Plant Lifetimes'!B3</f>
         <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B14">
-        <f>B6</f>
-        <v>25</v>
+        <f>B2</f>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B15">
-        <f>B11</f>
-        <v>40</v>
+        <f>B7</f>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B16">
-        <f>B11</f>
+        <f>B12</f>
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B17">
-        <f>B9</f>
+        <f>B12</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18">
+        <f>B10</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19">
+        <f>B2</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <f>B4</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21">
+        <f>B10</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22">
+        <f>B14</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23">
+        <f>B5</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24">
+        <f>B20</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25">
+        <f>B4</f>
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="B11" formulaRange="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>